--- a/data/Escenarios_Gx/160kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/160kW/elmo_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\160kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC1E062-7D8C-46F0-87BE-0CA1CF2F4D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE05BBD-E881-4E05-8EF2-146741F7DBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="200">
   <si>
     <t>id</t>
   </si>
@@ -637,6 +637,9 @@
   </si>
   <si>
     <t>0.1</t>
+  </si>
+  <si>
+    <t>h_max</t>
   </si>
 </sst>
 </file>
@@ -5381,13 +5384,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5412,8 +5415,11 @@
       <c r="H1" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5438,8 +5444,11 @@
       <c r="H2" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5463,6 +5472,9 @@
       </c>
       <c r="H3" s="3">
         <v>1000</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/Escenarios_Gx/160kW/elmo_data.xlsx
+++ b/data/Escenarios_Gx/160kW/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_Gx\160kW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_Gx\160kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE05BBD-E881-4E05-8EF2-146741F7DBCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CF4D6B-E68B-4310-B5D7-ED4C5AD42FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -1526,37 +1526,37 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.44140625" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="23" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.85546875" style="24" customWidth="1"/>
-    <col min="24" max="24" width="18.42578125" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.88671875" style="24" customWidth="1"/>
+    <col min="24" max="24" width="18.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="17" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="31">
         <v>1</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" s="31">
         <v>3</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" s="31">
         <v>4</v>
       </c>
@@ -2099,16 +2099,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>3</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>1</v>
       </c>
@@ -2195,9 +2195,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
         <v>3</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>1</v>
       </c>
@@ -2268,17 +2268,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H152"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.140625" style="69" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>3</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="52">
         <v>0</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53">
         <v>1</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53">
         <v>2</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="52">
         <v>3</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="53">
         <v>4</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="53">
         <v>5</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="52">
         <v>6</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="53">
         <v>7</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="53">
         <v>8</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="52">
         <v>9</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="53">
         <v>10</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="53">
         <v>11</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="53">
         <v>12</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="52">
         <v>13</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="53">
         <v>14</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="53">
         <v>15</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="52">
         <v>16</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="53">
         <v>17</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="53">
         <v>18</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="52">
         <v>19</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="53">
         <v>20</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>21</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="53">
         <v>22</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="52">
         <v>23</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="53">
         <v>24</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="52">
         <v>25</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="53">
         <v>26</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>27</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="52">
         <v>28</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>29</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="53">
         <v>30</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="52">
         <v>31</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="53">
         <v>32</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="53">
         <v>33</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="52">
         <v>34</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="53">
         <v>35</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="53">
         <v>36</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="53">
         <v>37</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="52">
         <v>38</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="53">
         <v>39</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="53">
         <v>40</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="53">
         <v>41</v>
       </c>
@@ -3422,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="53">
         <v>42</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="53">
         <v>43</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="53">
         <v>44</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="53">
         <v>45</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="53">
         <v>46</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="53">
         <v>47</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="53">
         <v>48</v>
       </c>
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="53">
         <v>49</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="53">
         <v>50</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="53">
         <v>51</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="53">
         <v>52</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="53">
         <v>53</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="53">
         <v>54</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="53">
         <v>55</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="53">
         <v>56</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="53">
         <v>57</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="53">
         <v>58</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="53">
         <v>59</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="53">
         <v>60</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="53">
         <v>61</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="53">
         <v>62</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="53">
         <v>63</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="53">
         <v>64</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="53">
         <v>65</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="53">
         <v>66</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="53">
         <v>67</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="53">
         <v>68</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="53">
         <v>69</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="53">
         <v>70</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="53">
         <v>71</v>
       </c>
@@ -4202,7 +4202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="53">
         <v>72</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="53">
         <v>73</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="53">
         <v>74</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="53">
         <v>75</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="53">
         <v>76</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="53">
         <v>77</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="53">
         <v>78</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="53">
         <v>79</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="53">
         <v>80</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="53">
         <v>81</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="53">
         <v>82</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="53">
         <v>83</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="53">
         <v>84</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="53">
         <v>85</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="53">
         <v>86</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="53">
         <v>87</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="53">
         <v>88</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="53">
         <v>89</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="53">
         <v>90</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="53">
         <v>91</v>
       </c>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="53">
         <v>92</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="53">
         <v>93</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -4783,7 +4783,7 @@
       <c r="F97"/>
       <c r="G97"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="54"/>
       <c r="B98" s="64"/>
       <c r="C98" s="61"/>
@@ -4791,7 +4791,7 @@
       <c r="G98" s="43"/>
       <c r="H98" s="44"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="55"/>
       <c r="B99" s="64"/>
       <c r="C99" s="62"/>
@@ -4799,7 +4799,7 @@
       <c r="G99" s="37"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="56"/>
       <c r="B100" s="64"/>
       <c r="C100" s="62"/>
@@ -4807,7 +4807,7 @@
       <c r="G100" s="37"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="57"/>
       <c r="B101" s="64"/>
       <c r="C101" s="62"/>
@@ -4815,7 +4815,7 @@
       <c r="G101" s="37"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="57"/>
       <c r="B102" s="64"/>
       <c r="C102" s="62"/>
@@ -4823,7 +4823,7 @@
       <c r="G102" s="37"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="57"/>
       <c r="B103" s="64"/>
       <c r="C103" s="62"/>
@@ -4831,7 +4831,7 @@
       <c r="G103" s="37"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="55"/>
       <c r="B104" s="64"/>
       <c r="C104" s="62"/>
@@ -4839,7 +4839,7 @@
       <c r="G104" s="37"/>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="56"/>
       <c r="B105" s="64"/>
       <c r="C105" s="62"/>
@@ -4847,7 +4847,7 @@
       <c r="G105" s="37"/>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="57"/>
       <c r="B106" s="64"/>
       <c r="C106" s="62"/>
@@ -4855,7 +4855,7 @@
       <c r="G106" s="37"/>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="57"/>
       <c r="B107" s="64"/>
       <c r="C107" s="62"/>
@@ -4863,7 +4863,7 @@
       <c r="G107" s="37"/>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="57"/>
       <c r="B108" s="64"/>
       <c r="C108" s="62"/>
@@ -4871,7 +4871,7 @@
       <c r="G108" s="37"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="55"/>
       <c r="B109" s="64"/>
       <c r="C109" s="62"/>
@@ -4879,7 +4879,7 @@
       <c r="G109" s="37"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="56"/>
       <c r="B110" s="64"/>
       <c r="C110" s="62"/>
@@ -4887,7 +4887,7 @@
       <c r="G110" s="37"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="57"/>
       <c r="B111" s="64"/>
       <c r="C111" s="62"/>
@@ -4895,7 +4895,7 @@
       <c r="G111" s="37"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="57"/>
       <c r="B112" s="64"/>
       <c r="C112" s="62"/>
@@ -4903,7 +4903,7 @@
       <c r="G112" s="37"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="57"/>
       <c r="B113" s="64"/>
       <c r="C113" s="62"/>
@@ -4911,7 +4911,7 @@
       <c r="G113" s="37"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="55"/>
       <c r="B114" s="64"/>
       <c r="C114" s="62"/>
@@ -4919,7 +4919,7 @@
       <c r="G114" s="37"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="56"/>
       <c r="B115" s="64"/>
       <c r="C115" s="62"/>
@@ -4927,7 +4927,7 @@
       <c r="G115" s="37"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="57"/>
       <c r="B116" s="64"/>
       <c r="C116" s="62"/>
@@ -4935,7 +4935,7 @@
       <c r="G116" s="37"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="57"/>
       <c r="B117" s="64"/>
       <c r="C117" s="62"/>
@@ -4943,7 +4943,7 @@
       <c r="G117" s="37"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="57"/>
       <c r="B118" s="64"/>
       <c r="C118" s="62"/>
@@ -4951,7 +4951,7 @@
       <c r="G118" s="37"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="55"/>
       <c r="B119" s="64"/>
       <c r="C119" s="62"/>
@@ -4959,7 +4959,7 @@
       <c r="G119" s="37"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="56"/>
       <c r="B120" s="64"/>
       <c r="C120" s="62"/>
@@ -4967,7 +4967,7 @@
       <c r="G120" s="37"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="57"/>
       <c r="B121" s="64"/>
       <c r="C121" s="62"/>
@@ -4975,7 +4975,7 @@
       <c r="G121" s="37"/>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="57"/>
       <c r="B122" s="64"/>
       <c r="C122" s="62"/>
@@ -4983,7 +4983,7 @@
       <c r="G122" s="37"/>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="57"/>
       <c r="B123" s="64"/>
       <c r="C123" s="62"/>
@@ -4991,7 +4991,7 @@
       <c r="G123" s="37"/>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="55"/>
       <c r="B124" s="64"/>
       <c r="C124" s="62"/>
@@ -4999,7 +4999,7 @@
       <c r="G124" s="37"/>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="56"/>
       <c r="B125" s="64"/>
       <c r="C125" s="62"/>
@@ -5007,7 +5007,7 @@
       <c r="G125" s="37"/>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="57"/>
       <c r="B126" s="64"/>
       <c r="C126" s="62"/>
@@ -5015,7 +5015,7 @@
       <c r="G126" s="37"/>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="57"/>
       <c r="B127" s="64"/>
       <c r="C127" s="62"/>
@@ -5023,7 +5023,7 @@
       <c r="G127" s="37"/>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="57"/>
       <c r="B128" s="64"/>
       <c r="C128" s="62"/>
@@ -5031,7 +5031,7 @@
       <c r="G128" s="37"/>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="55"/>
       <c r="B129" s="64"/>
       <c r="C129" s="62"/>
@@ -5039,7 +5039,7 @@
       <c r="G129" s="37"/>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="56"/>
       <c r="B130" s="64"/>
       <c r="C130" s="62"/>
@@ -5047,7 +5047,7 @@
       <c r="G130" s="37"/>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="57"/>
       <c r="B131" s="64"/>
       <c r="C131" s="62"/>
@@ -5055,7 +5055,7 @@
       <c r="G131" s="37"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="57"/>
       <c r="B132" s="64"/>
       <c r="C132" s="62"/>
@@ -5063,7 +5063,7 @@
       <c r="G132" s="37"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="57"/>
       <c r="B133" s="64"/>
       <c r="C133" s="62"/>
@@ -5071,7 +5071,7 @@
       <c r="G133" s="37"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="55"/>
       <c r="B134" s="64"/>
       <c r="C134" s="62"/>
@@ -5079,7 +5079,7 @@
       <c r="G134" s="37"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="56"/>
       <c r="B135" s="64"/>
       <c r="C135" s="62"/>
@@ -5087,7 +5087,7 @@
       <c r="G135" s="37"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="57"/>
       <c r="B136" s="64"/>
       <c r="C136" s="62"/>
@@ -5095,7 +5095,7 @@
       <c r="G136" s="37"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="57"/>
       <c r="B137" s="64"/>
       <c r="C137" s="62"/>
@@ -5103,7 +5103,7 @@
       <c r="G137" s="37"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="57"/>
       <c r="B138" s="64"/>
       <c r="C138" s="62"/>
@@ -5111,7 +5111,7 @@
       <c r="G138" s="37"/>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="55"/>
       <c r="B139" s="64"/>
       <c r="C139" s="62"/>
@@ -5119,7 +5119,7 @@
       <c r="G139" s="37"/>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="56"/>
       <c r="B140" s="64"/>
       <c r="C140" s="62"/>
@@ -5127,7 +5127,7 @@
       <c r="G140" s="37"/>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="57"/>
       <c r="B141" s="64"/>
       <c r="C141" s="62"/>
@@ -5135,7 +5135,7 @@
       <c r="G141" s="37"/>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="57"/>
       <c r="B142" s="64"/>
       <c r="C142" s="62"/>
@@ -5143,7 +5143,7 @@
       <c r="G142" s="37"/>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="57"/>
       <c r="B143" s="64"/>
       <c r="C143" s="62"/>
@@ -5151,7 +5151,7 @@
       <c r="G143" s="37"/>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="55"/>
       <c r="B144" s="64"/>
       <c r="C144" s="62"/>
@@ -5159,7 +5159,7 @@
       <c r="G144" s="37"/>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="56"/>
       <c r="B145" s="64"/>
       <c r="C145" s="62"/>
@@ -5167,7 +5167,7 @@
       <c r="G145" s="37"/>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="57"/>
       <c r="B146" s="64"/>
       <c r="C146" s="62"/>
@@ -5175,7 +5175,7 @@
       <c r="G146" s="37"/>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="57"/>
       <c r="B147" s="64"/>
       <c r="C147" s="62"/>
@@ -5183,7 +5183,7 @@
       <c r="G147" s="37"/>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="57"/>
       <c r="B148" s="64"/>
       <c r="C148" s="62"/>
@@ -5191,7 +5191,7 @@
       <c r="G148" s="37"/>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="55"/>
       <c r="B149" s="64"/>
       <c r="C149" s="62"/>
@@ -5199,7 +5199,7 @@
       <c r="G149" s="37"/>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="56"/>
       <c r="B150" s="64"/>
       <c r="C150" s="62"/>
@@ -5207,7 +5207,7 @@
       <c r="G150" s="37"/>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="57"/>
       <c r="B151" s="64"/>
       <c r="C151" s="62"/>
@@ -5215,7 +5215,7 @@
       <c r="G151" s="37"/>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="57"/>
       <c r="B152" s="64"/>
       <c r="C152" s="62"/>
@@ -5235,14 +5235,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5253,7 +5253,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -5283,9 +5283,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903B846-9155-4C37-ABE1-59FA4D45CD76}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -5385,12 +5385,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{387AF5AC-D97C-4B95-B84B-AE3277E9ED2E}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5419,7 +5419,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -5485,15 +5485,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB361D3-2C0F-481F-8505-844CB2F9BDD0}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="73">
         <v>1</v>
       </c>
